--- a/Documentation/Shaders-Summary.xlsx
+++ b/Documentation/Shaders-Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qesrg\Desktop\CG\3D-Data-Visualizer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qesrg\Desktop\CG\3D-Data-Visualizer\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B8635A-1C11-43D3-968B-D074D48CD0A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BE8AA3-51D2-4845-8B64-D001456794B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21468231-176E-4380-A623-6D9DD4C234A8}"/>
   </bookViews>
@@ -101,16 +101,6 @@
     <t>dot_frag.glsl</t>
   </si>
   <si>
-    <t>int mode;
-vec3 cameraPos;
-float renderHeight;
-float minDistanceToCamera;
-float maxDistanceToCamera; sampler2D colorMap;</t>
-  </si>
-  <si>
-    <t>Outputs the dot color based on the rendering mode, the vertex position and the camera position.</t>
-  </si>
-  <si>
     <t>line_geometry.glsl</t>
   </si>
   <si>
@@ -339,6 +329,18 @@
   </si>
   <si>
     <t>Renders a rectangle on the screen showing the color map used.</t>
+  </si>
+  <si>
+    <t>int mode;
+vec3 cameraPos;
+sampler2D normalMap;                sampler2D colorMap;                   sampler2D edgeMap;
+float renderSize;
+float renderHeight;
+float minDistanceToCamera;
+float maxDistanceToCamera;</t>
+  </si>
+  <si>
+    <t>Outputs the dot color based on the rendering mode, the vertex position and the camera position. It creates a darkening gradient for the points based on the distance to the camera.</t>
   </si>
 </sst>
 </file>
@@ -513,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -539,9 +541,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -554,15 +553,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -581,112 +632,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -751,6 +725,28 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -765,15 +761,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45837B21-952A-42F7-A184-D1C088978F79}" name="Table2" displayName="Table2" ref="B5:G19" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{45837B21-952A-42F7-A184-D1C088978F79}" name="Table2" displayName="Table2" ref="B5:G19" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="B5:G19" xr:uid="{45837B21-952A-42F7-A184-D1C088978F79}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C1435FBE-8440-4624-BDC1-997586E0E827}" name="Column1" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{6F4DC806-1105-4935-8234-822A1C29A65A}" name="Shader Type" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{3A83544D-9702-46C8-A184-E851432C6C02}" name="Input from previous shader" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{ADFA99B0-EB0B-4A6C-B5D9-2EB35DE2C8F3}" name="Uniform Input" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{3604638E-C756-48F1-B33D-05F5C1E142DC}" name="Output" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{EA5B21C6-28E8-4CB9-A0EC-A34B66EC9B43}" name="Small Description" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C1435FBE-8440-4624-BDC1-997586E0E827}" name="Column1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{6F4DC806-1105-4935-8234-822A1C29A65A}" name="Shader Type" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{3A83544D-9702-46C8-A184-E851432C6C02}" name="Input from previous shader" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{ADFA99B0-EB0B-4A6C-B5D9-2EB35DE2C8F3}" name="Uniform Input" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{3604638E-C756-48F1-B33D-05F5C1E142DC}" name="Output" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{EA5B21C6-28E8-4CB9-A0EC-A34B66EC9B43}" name="Small Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1110,27 +1106,27 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="19"/>
+      <c r="B2" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="36"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="20"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="22"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="39"/>
     </row>
     <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>0</v>
@@ -1149,281 +1145,281 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="2:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="14" t="s">
+      <c r="C10" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
+      <c r="D10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="12" t="s">
         <v>24</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="13" t="s">
-        <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="13" t="s">
-        <v>27</v>
+      <c r="B12" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="24" x14ac:dyDescent="0.25">
+      <c r="B13" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
-        <v>35</v>
+      <c r="B14" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="14" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="15" spans="2:7" ht="180" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
-        <v>36</v>
+      <c r="B15" s="12" t="s">
+        <v>34</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="E15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="14" t="s">
-        <v>42</v>
+      <c r="G15" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
-        <v>43</v>
+      <c r="B16" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>44</v>
+      <c r="F16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="270" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
-        <v>45</v>
+      <c r="B17" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="14" t="s">
+      <c r="D17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="G17" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="18" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>47</v>
+      <c r="B18" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="9" t="s">
+      <c r="D18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>56</v>
+      <c r="D19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
@@ -1459,22 +1455,22 @@
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
+      <c r="B24" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="36"/>
     </row>
     <row r="25" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="22"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="39"/>
     </row>
     <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
@@ -1486,156 +1482,156 @@
     </row>
     <row r="27" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
-      <c r="C27" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
+      <c r="C27" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
       <c r="G27" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="42" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="32" t="s">
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C30" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="35" t="s">
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="28" t="s">
+    <row r="31" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B31" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C31" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="25" t="s">
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="15" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="36" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C32" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="39" t="s">
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="23" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B31" s="28" t="s">
+    <row r="33" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B33" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C33" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="25" t="s">
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="15" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="40" t="s">
+    <row r="34" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B34" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C34" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43" t="s">
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" s="29" t="s">
+    <row r="35" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C35" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="25" t="s">
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="40" t="s">
+    <row r="36" spans="2:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="44" t="s">
+      <c r="C36" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="39" t="s">
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="25" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="25" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="46" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="49" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="B24:G25"/>
+    <mergeCell ref="B2:G3"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C36:F36"/>
-    <mergeCell ref="B24:G25"/>
-    <mergeCell ref="B2:G3"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Documentation/Shaders-Summary.xlsx
+++ b/Documentation/Shaders-Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qesrg\Desktop\CG\3D-Data-Visualizer\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30BE8AA3-51D2-4845-8B64-D001456794B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36776BE-14C9-4449-894B-877BDCBD3303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21468231-176E-4380-A623-6D9DD4C234A8}"/>
   </bookViews>
@@ -591,6 +591,48 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -613,48 +655,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1092,6 +1092,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1983EE3C-D493-4059-B49D-A64E57E2F103}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:G36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1106,22 +1109,22 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="32"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="39"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="35"/>
     </row>
     <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1455,22 +1458,22 @@
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="36"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="37"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="39"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="35"/>
     </row>
     <row r="26" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3"/>
@@ -1482,12 +1485,12 @@
     </row>
     <row r="27" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3"/>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
       <c r="G27" s="7" t="s">
         <v>67</v>
       </c>
@@ -1496,12 +1499,12 @@
       <c r="B28" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
       <c r="G28" s="19" t="s">
         <v>78</v>
       </c>
@@ -1510,12 +1513,12 @@
       <c r="B29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
       <c r="G29" s="15" t="s">
         <v>79</v>
       </c>
@@ -1524,12 +1527,12 @@
       <c r="B30" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
       <c r="G30" s="21" t="s">
         <v>80</v>
       </c>
@@ -1538,12 +1541,12 @@
       <c r="B31" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="C31" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
       <c r="G31" s="15" t="s">
         <v>81</v>
       </c>
@@ -1552,12 +1555,12 @@
       <c r="B32" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41"/>
+      <c r="F32" s="41"/>
       <c r="G32" s="23" t="s">
         <v>82</v>
       </c>
@@ -1566,12 +1569,12 @@
       <c r="B33" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="42" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
       <c r="G33" s="15" t="s">
         <v>83</v>
       </c>
@@ -1580,12 +1583,12 @@
       <c r="B34" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
       <c r="G34" s="21" t="s">
         <v>84</v>
       </c>
@@ -1594,12 +1597,12 @@
       <c r="B35" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="43"/>
       <c r="G35" s="15" t="s">
         <v>85</v>
       </c>
@@ -1608,18 +1611,23 @@
       <c r="B36" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
       <c r="G36" s="25" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B24:G25"/>
@@ -1627,15 +1635,11 @@
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>